--- a/benchmarking/evaluation_results/excel/link_deletion.xlsx
+++ b/benchmarking/evaluation_results/excel/link_deletion.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="0.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="0.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="0.1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="0.2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="0.3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,28 +482,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="E2" t="n">
         <v>0.0001</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.00029</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00029</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0022</v>
+        <v>0.00029</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.00019</v>
       </c>
       <c r="I2" t="n">
         <v>0.0001</v>
@@ -510,205 +511,205 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.00125</v>
+        <v>0.00038</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00057</v>
+        <v>0.00048</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00067</v>
+        <v>0.00048</v>
       </c>
       <c r="D3" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.00115</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.00019</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.00259</v>
-      </c>
       <c r="H3" t="n">
-        <v>0.00029</v>
+        <v>0.00048</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00019</v>
+        <v>0.00038</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.00163</v>
+        <v>0.00048</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0023</v>
+        <v>0.00086</v>
       </c>
       <c r="C4" t="n">
         <v>0.00067</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00144</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.00038</v>
+        <v>0.00057</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.00383</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00029</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.00278</v>
+        <v>0.00182</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.00201</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00029</v>
+        <v>0.00077</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00029</v>
+        <v>0.00057</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.00642</v>
+        <v>0.00182</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00671</v>
+        <v>0.00172</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00163</v>
+        <v>0.0045</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00297</v>
-      </c>
-      <c r="E5" t="n">
         <v>0.00057</v>
       </c>
+      <c r="E5" s="2" t="n">
+        <v>0.00623</v>
+      </c>
       <c r="F5" t="n">
-        <v>0.00096</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.00747</v>
+        <v>0.00211</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.00316</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00115</v>
+        <v>0.00105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00086</v>
+        <v>0.00153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1025</v>
+        <v>2510</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>2479</v>
       </c>
       <c r="C6" t="n">
-        <v>1511</v>
+        <v>2380</v>
       </c>
       <c r="D6" t="n">
-        <v>1034</v>
+        <v>2548</v>
       </c>
       <c r="E6" t="n">
-        <v>1538</v>
+        <v>1954</v>
       </c>
       <c r="F6" t="n">
-        <v>1223</v>
+        <v>2537</v>
       </c>
       <c r="G6" t="n">
-        <v>1030</v>
+        <v>2563</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1576</v>
+        <v>3141</v>
       </c>
       <c r="I6" t="n">
-        <v>1183</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1025</v>
+        <v>2510</v>
       </c>
       <c r="B7" t="n">
-        <v>999</v>
+        <v>2479</v>
       </c>
       <c r="C7" t="n">
-        <v>1511</v>
+        <v>2380</v>
       </c>
       <c r="D7" t="n">
-        <v>1034</v>
+        <v>2548</v>
       </c>
       <c r="E7" t="n">
-        <v>1538</v>
+        <v>1954</v>
       </c>
       <c r="F7" t="n">
-        <v>1223</v>
+        <v>2537</v>
       </c>
       <c r="G7" t="n">
-        <v>1030</v>
+        <v>2563</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1576</v>
+        <v>3141</v>
       </c>
       <c r="I7" t="n">
-        <v>1183</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.00362</v>
+        <v>0.00162</v>
       </c>
       <c r="B8" t="n">
-        <v>0.00406</v>
+        <v>0.00181</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00157</v>
+        <v>0.00306</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00343</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.00102</v>
+        <v>0.00136</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.00405</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00198</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0.00613</v>
+        <v>0.00204</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.00229</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00114</v>
+        <v>0.00115</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00234</v>
+        <v>0.00161</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.00362</v>
+        <v>0.00162</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00406</v>
+        <v>0.00181</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00157</v>
+        <v>0.00306</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00343</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.00102</v>
+        <v>0.00136</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.00405</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00198</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.00613</v>
+        <v>0.00204</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.00229</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00114</v>
+        <v>0.00115</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00234</v>
+        <v>0.00161</v>
       </c>
     </row>
   </sheetData>
@@ -774,234 +775,234 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
         <v>0.0001</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.00019</v>
-      </c>
       <c r="C2" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="E2" t="n">
         <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00019</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.00067</v>
       </c>
       <c r="F2" t="n">
         <v>0.0001</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.00057</v>
+      <c r="G2" s="2" t="n">
+        <v>0.0022</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.0001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.00077</v>
+        <v>0.00125</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00144</v>
+        <v>0.00057</v>
       </c>
       <c r="C3" t="n">
+        <v>0.00067</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.00019</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.00872</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.00086</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.00096</v>
+      <c r="G3" s="2" t="n">
+        <v>0.00259</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001</v>
+        <v>0.00029</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00096</v>
+        <v>0.00019</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.00125</v>
+        <v>0.00163</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00402</v>
+        <v>0.0023</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00019</v>
+        <v>0.00067</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00316</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.02548</v>
+        <v>0.00144</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.00038</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00201</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.00307</v>
+        <v>0.00029</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.00278</v>
       </c>
       <c r="H4" t="n">
         <v>0.00029</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00163</v>
+        <v>0.00029</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.00345</v>
+        <v>0.00642</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00613</v>
+        <v>0.00671</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00144</v>
+        <v>0.00163</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00479</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.03813</v>
+        <v>0.00297</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.00057</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00374</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.00383</v>
+        <v>0.00096</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.00747</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00057</v>
+        <v>0.00115</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0024</v>
+        <v>0.00086</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1212</v>
+        <v>1025</v>
       </c>
       <c r="B6" t="n">
-        <v>1161</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>1219</v>
+        <v>1511</v>
       </c>
       <c r="D6" t="n">
-        <v>1137</v>
+        <v>1034</v>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>1538</v>
       </c>
       <c r="F6" t="n">
-        <v>1147</v>
+        <v>1223</v>
       </c>
       <c r="G6" t="n">
-        <v>1165</v>
+        <v>1030</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1723</v>
+        <v>1576</v>
       </c>
       <c r="I6" t="n">
-        <v>1175</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1212</v>
+        <v>1025</v>
       </c>
       <c r="B7" t="n">
-        <v>1161</v>
+        <v>999</v>
       </c>
       <c r="C7" t="n">
-        <v>1219</v>
+        <v>1511</v>
       </c>
       <c r="D7" t="n">
-        <v>1137</v>
+        <v>1034</v>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>1538</v>
       </c>
       <c r="F7" t="n">
-        <v>1147</v>
+        <v>1223</v>
       </c>
       <c r="G7" t="n">
-        <v>1165</v>
+        <v>1030</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1723</v>
+        <v>1576</v>
       </c>
       <c r="I7" t="n">
-        <v>1175</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0027</v>
+        <v>0.00362</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0036</v>
+        <v>0.00406</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00252</v>
+        <v>0.00157</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00405</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0.01483</v>
+        <v>0.00343</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.00102</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00312</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.00378</v>
+        <v>0.00198</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.00613</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00106</v>
+        <v>0.00114</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00304</v>
+        <v>0.00234</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0027</v>
+        <v>0.00362</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0036</v>
+        <v>0.00406</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00252</v>
+        <v>0.00157</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00405</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.01483</v>
+        <v>0.00343</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00102</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00312</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.00378</v>
+        <v>0.00198</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.00613</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00106</v>
+        <v>0.00114</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00304</v>
+        <v>0.00234</v>
       </c>
     </row>
   </sheetData>
@@ -1067,234 +1068,234 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="B2" t="n">
         <v>0.00019</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0.00163</v>
-      </c>
       <c r="C2" t="n">
-        <v>0.00048</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00038</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.00038</v>
+        <v>0.00019</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.00067</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00019</v>
+        <v>0.0001</v>
       </c>
       <c r="G2" t="n">
+        <v>0.00057</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.0001</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.00163</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0.00489</v>
+        <v>0.00077</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.00144</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00067</v>
+        <v>0.00019</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00077</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.00268</v>
+        <v>0.0022</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.00872</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00278</v>
+        <v>0.00086</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00153</v>
+        <v>0.00096</v>
       </c>
       <c r="H3" t="n">
         <v>0.0001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00048</v>
+        <v>0.00096</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.00316</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.00201</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.00307</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.00163</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.00795</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.00077</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.00125</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.01313</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.00383</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.00192</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.00019</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.00067</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.00335</v>
+        <v>0.00345</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01265</v>
+        <v>0.00613</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00163</v>
+        <v>0.00144</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00268</v>
+        <v>0.00479</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.01485</v>
+        <v>0.03813</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00594</v>
+        <v>0.00374</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00469</v>
+        <v>0.00383</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00048</v>
+        <v>0.00057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00249</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1281</v>
+        <v>1212</v>
       </c>
       <c r="B6" t="n">
-        <v>1245</v>
+        <v>1161</v>
       </c>
       <c r="C6" t="n">
-        <v>1956</v>
+        <v>1219</v>
       </c>
       <c r="D6" t="n">
-        <v>1326</v>
+        <v>1137</v>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F6" t="n">
-        <v>1264</v>
+        <v>1147</v>
       </c>
       <c r="G6" t="n">
-        <v>1362</v>
+        <v>1165</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1992</v>
+        <v>1723</v>
       </c>
       <c r="I6" t="n">
-        <v>1357</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1281</v>
+        <v>1212</v>
       </c>
       <c r="B7" t="n">
-        <v>1245</v>
+        <v>1161</v>
       </c>
       <c r="C7" t="n">
-        <v>1956</v>
+        <v>1219</v>
       </c>
       <c r="D7" t="n">
-        <v>1326</v>
+        <v>1137</v>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F7" t="n">
-        <v>1264</v>
+        <v>1147</v>
       </c>
       <c r="G7" t="n">
-        <v>1362</v>
+        <v>1165</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1992</v>
+        <v>1723</v>
       </c>
       <c r="I7" t="n">
-        <v>1357</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.00315</v>
+        <v>0.0027</v>
       </c>
       <c r="B8" t="n">
-        <v>0.009480000000000001</v>
+        <v>0.0036</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00161</v>
+        <v>0.00252</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00314</v>
+        <v>0.00405</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.009480000000000001</v>
+        <v>0.01483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00385</v>
+        <v>0.00312</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00306</v>
+        <v>0.00378</v>
       </c>
       <c r="H8" t="n">
         <v>0.00106</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00243</v>
+        <v>0.00304</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.00315</v>
+        <v>0.0027</v>
       </c>
       <c r="B9" t="n">
-        <v>0.009480000000000001</v>
+        <v>0.0036</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00161</v>
+        <v>0.00252</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00314</v>
+        <v>0.00405</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.009480000000000001</v>
+        <v>0.01483</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00385</v>
+        <v>0.00312</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00306</v>
+        <v>0.00378</v>
       </c>
       <c r="H9" t="n">
         <v>0.00106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00243</v>
+        <v>0.00304</v>
       </c>
     </row>
   </sheetData>
@@ -1360,6 +1361,299 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.00048</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.00489</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.00067</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.00077</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.00278</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.00048</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00077</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.01313</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.00383</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.00192</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.00067</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.00335</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.01265</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.01485</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.00594</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.00469</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.00048</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.00249</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1281</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1245</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1956</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1326</v>
+      </c>
+      <c r="E6" t="n">
+        <v>864</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1264</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1362</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1281</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1245</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1956</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1326</v>
+      </c>
+      <c r="E7" t="n">
+        <v>864</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1264</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1362</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.00315</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.009480000000000001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.00161</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.00314</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.009480000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.00385</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.00243</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.00315</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.009480000000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.00161</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.00314</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.009480000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.00385</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.00243</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TransE</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DistMult</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ComplEx</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>HolE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ConvE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PairRE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>AutoSF</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>BoxE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>RotatE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
